--- a/hall/resources/sample/VisitorGenPaid.xlsx
+++ b/hall/resources/sample/VisitorGenPaid.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="VisitorGenPaid" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>序号ID</t>
   </si>
@@ -104,9 +104,6 @@
     <t>价格类型</t>
   </si>
   <si>
-    <t>价格数量</t>
-  </si>
-  <si>
     <t>价格数量1</t>
   </si>
   <si>
@@ -119,9 +116,6 @@
     <t>int</t>
   </si>
   <si>
-    <t>list&lt;int&gt;{_}</t>
-  </si>
-  <si>
     <t>BigDecimal</t>
   </si>
   <si>
@@ -140,9 +134,6 @@
     <t>CostType</t>
   </si>
   <si>
-    <t>PriceValue</t>
-  </si>
-  <si>
     <t>PriceValue1</t>
   </si>
   <si>
@@ -155,9 +146,6 @@
     <t>文艺青年</t>
   </si>
   <si>
-    <t>1980000_100</t>
-  </si>
-  <si>
     <t>书香少女</t>
   </si>
   <si>
@@ -167,13 +155,7 @@
     <t>独立画家</t>
   </si>
   <si>
-    <t>1980000_200</t>
-  </si>
-  <si>
     <t>古典乐迷</t>
-  </si>
-  <si>
-    <t>1980000_500</t>
   </si>
   <si>
     <t>科技极客</t>
@@ -1395,19 +1377,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="14.375" customWidth="1"/>
     <col min="4" max="4" width="13.25" customWidth="1"/>
     <col min="5" max="5" width="12.75" customWidth="1"/>
-    <col min="6" max="6" width="16.875" customWidth="1"/>
-    <col min="7" max="7" width="12.5" customWidth="1"/>
-    <col min="8" max="8" width="17.875" customWidth="1"/>
-    <col min="9" max="9" width="15.625" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="7" max="7" width="17.875" customWidth="1"/>
+    <col min="8" max="8" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1429,66 +1410,57 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="H2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="B3" t="s">
         <v>12</v>
       </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:9">
+    <row r="5" ht="16.5" spans="1:8">
       <c r="A5">
         <v>101</v>
       </c>
@@ -1496,7 +1468,7 @@
         <v>1025304</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1504,11 +1476,11 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" t="s">
-        <v>22</v>
+      <c r="F5">
+        <v>100</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:9">
+    <row r="6" ht="16.5" spans="1:8">
       <c r="A6">
         <v>102</v>
       </c>
@@ -1516,7 +1488,7 @@
         <v>1025305</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1524,11 +1496,11 @@
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
-        <v>22</v>
+      <c r="F6">
+        <v>100</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:9">
+    <row r="7" ht="16.5" spans="1:8">
       <c r="A7">
         <v>103</v>
       </c>
@@ -1536,7 +1508,7 @@
         <v>1025405</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1544,11 +1516,11 @@
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7" t="s">
-        <v>22</v>
+      <c r="F7">
+        <v>100</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:9">
+    <row r="8" ht="16.5" spans="1:8">
       <c r="A8">
         <v>104</v>
       </c>
@@ -1556,7 +1528,7 @@
         <v>1025404</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1564,11 +1536,11 @@
       <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8" t="s">
-        <v>26</v>
+      <c r="F8">
+        <v>200</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:9">
+    <row r="9" ht="16.5" spans="1:8">
       <c r="A9">
         <v>105</v>
       </c>
@@ -1576,7 +1548,7 @@
         <v>1025405</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1584,11 +1556,11 @@
       <c r="E9">
         <v>1</v>
       </c>
-      <c r="F9" t="s">
-        <v>26</v>
+      <c r="F9">
+        <v>200</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:9">
+    <row r="10" ht="16.5" spans="1:8">
       <c r="A10">
         <v>106</v>
       </c>
@@ -1596,7 +1568,7 @@
         <v>1025406</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1604,11 +1576,11 @@
       <c r="E10">
         <v>1</v>
       </c>
-      <c r="F10" t="s">
-        <v>28</v>
+      <c r="F10">
+        <v>500</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:9">
+    <row r="11" ht="16.5" spans="1:8">
       <c r="A11">
         <v>201</v>
       </c>
@@ -1616,7 +1588,7 @@
         <v>1025403</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1624,14 +1596,14 @@
       <c r="E11">
         <v>2</v>
       </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
       <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="16.5" spans="1:9">
+    <row r="12" ht="16.5" spans="1:8">
       <c r="A12">
         <v>202</v>
       </c>
@@ -1639,7 +1611,7 @@
         <v>1025501</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1647,14 +1619,14 @@
       <c r="E12">
         <v>2</v>
       </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
       <c r="G12">
-        <v>2</v>
-      </c>
-      <c r="H12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" ht="16.5" spans="1:9">
+    <row r="13" ht="16.5" spans="1:8">
       <c r="A13">
         <v>203</v>
       </c>
@@ -1662,7 +1634,7 @@
         <v>1025502</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1670,14 +1642,14 @@
       <c r="E13">
         <v>2</v>
       </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
       <c r="G13">
-        <v>3</v>
-      </c>
-      <c r="H13">
         <v>10</v>
       </c>
     </row>
-    <row r="14" ht="16.5" spans="1:9">
+    <row r="14" ht="16.5" spans="1:8">
       <c r="A14">
         <v>204</v>
       </c>
@@ -1685,7 +1657,7 @@
         <v>1025503</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1693,14 +1665,14 @@
       <c r="E14">
         <v>2</v>
       </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
       <c r="G14">
-        <v>4</v>
-      </c>
-      <c r="H14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" ht="16.5" spans="1:9">
+    <row r="15" ht="16.5" spans="1:8">
       <c r="A15">
         <v>205</v>
       </c>
@@ -1708,7 +1680,7 @@
         <v>1025504</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1716,10 +1688,10 @@
       <c r="E15">
         <v>2</v>
       </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
       <c r="G15">
-        <v>5</v>
-      </c>
-      <c r="H15">
         <v>10</v>
       </c>
     </row>

--- a/hall/resources/sample/VisitorGenPaid.xlsx
+++ b/hall/resources/sample/VisitorGenPaid.xlsx
@@ -37,7 +37,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="54">
   <si>
     <t>序号ID</t>
   </si>
@@ -98,6 +98,9 @@
     <t>名称备注</t>
   </si>
   <si>
+    <t>品质备注</t>
+  </si>
+  <si>
     <t>单个游客数量</t>
   </si>
   <si>
@@ -143,27 +146,96 @@
     <t>icon</t>
   </si>
   <si>
+    <t>街头潮人</t>
+  </si>
+  <si>
+    <t>白</t>
+  </si>
+  <si>
+    <t>复古绅士</t>
+  </si>
+  <si>
+    <t>酷盖少年</t>
+  </si>
+  <si>
+    <t>潮流先锋</t>
+  </si>
+  <si>
+    <t>时尚教主</t>
+  </si>
+  <si>
+    <t>街拍达人</t>
+  </si>
+  <si>
+    <t>运动健将</t>
+  </si>
+  <si>
+    <t>绿</t>
+  </si>
+  <si>
+    <t>跑酷少年</t>
+  </si>
+  <si>
+    <t>滑板高手</t>
+  </si>
+  <si>
+    <t>甜心辣妹</t>
+  </si>
+  <si>
+    <t>活力少女</t>
+  </si>
+  <si>
+    <t>优雅女神</t>
+  </si>
+  <si>
+    <t>健身狂魔</t>
+  </si>
+  <si>
+    <t>蓝</t>
+  </si>
+  <si>
+    <t>单车骑士</t>
+  </si>
+  <si>
+    <t>登山行者</t>
+  </si>
+  <si>
     <t>文艺青年</t>
   </si>
   <si>
     <t>书香少女</t>
   </si>
   <si>
+    <t>民谣歌手</t>
+  </si>
+  <si>
+    <t>马拉松客</t>
+  </si>
+  <si>
+    <t>紫</t>
+  </si>
+  <si>
+    <t>极限玩家</t>
+  </si>
+  <si>
+    <t>科技极客</t>
+  </si>
+  <si>
+    <t>独立画家</t>
+  </si>
+  <si>
     <t>浪漫诗人</t>
   </si>
   <si>
-    <t>独立画家</t>
-  </si>
-  <si>
     <t>古典乐迷</t>
   </si>
   <si>
-    <t>科技极客</t>
-  </si>
-  <si>
     <t>创业新贵</t>
   </si>
   <si>
+    <t>金</t>
+  </si>
+  <si>
     <t>摸金校尉</t>
   </si>
   <si>
@@ -171,6 +243,12 @@
   </si>
   <si>
     <t>穿搭博主</t>
+  </si>
+  <si>
+    <t>美妆新秀</t>
+  </si>
+  <si>
+    <t>高定女王</t>
   </si>
 </sst>
 </file>
@@ -183,7 +261,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,12 +274,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -699,137 +771,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -839,10 +911,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1377,18 +1452,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="14.375" customWidth="1"/>
-    <col min="4" max="4" width="13.25" customWidth="1"/>
-    <col min="5" max="5" width="12.75" customWidth="1"/>
-    <col min="6" max="6" width="12.5" customWidth="1"/>
-    <col min="7" max="7" width="17.875" customWidth="1"/>
-    <col min="8" max="8" width="15.625" customWidth="1"/>
+    <col min="4" max="5" width="13.25" customWidth="1"/>
+    <col min="6" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="7" width="12.5" customWidth="1"/>
+    <col min="8" max="8" width="17.875" customWidth="1"/>
+    <col min="9" max="9" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1410,41 +1485,41 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
         <v>13</v>
       </c>
       <c r="E3" t="s">
@@ -1456,253 +1531,726 @@
       <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:8">
-      <c r="A5">
+      <c r="I3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:9">
+      <c r="A5" s="3">
         <v>101</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
+        <v>1025101</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:9">
+      <c r="A6" s="3">
+        <v>102</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1025102</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:9">
+      <c r="A7" s="3">
+        <v>103</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1025103</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:9">
+      <c r="A8" s="3">
+        <v>104</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1025104</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:9">
+      <c r="A9" s="3">
+        <v>105</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1025105</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:9">
+      <c r="A10" s="3">
+        <v>106</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1025106</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:9">
+      <c r="A11" s="3">
+        <v>107</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1025201</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:9">
+      <c r="A12" s="3">
+        <v>108</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1025202</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:9">
+      <c r="A13" s="3">
+        <v>109</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1025203</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:9">
+      <c r="A14" s="3">
+        <v>110</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1025204</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:9">
+      <c r="A15" s="3">
+        <v>111</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1025205</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:9">
+      <c r="A16" s="3">
+        <v>112</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1025206</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:8">
+      <c r="A17" s="3">
+        <v>113</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1025301</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:8">
+      <c r="A18" s="3">
+        <v>114</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1025302</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18">
+        <v>10</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:8">
+      <c r="A19" s="3">
+        <v>115</v>
+      </c>
+      <c r="B19" s="4">
+        <v>1025303</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19">
+        <v>10</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:8">
+      <c r="A20" s="3">
+        <v>116</v>
+      </c>
+      <c r="B20" s="4">
         <v>1025304</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:8">
-      <c r="A6">
-        <v>102</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="C20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20">
+        <v>10</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:8">
+      <c r="A21" s="3">
+        <v>117</v>
+      </c>
+      <c r="B21" s="4">
         <v>1025305</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:8">
-      <c r="A7">
-        <v>103</v>
-      </c>
-      <c r="B7" s="3">
+      <c r="C21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:8">
+      <c r="A22" s="3">
+        <v>118</v>
+      </c>
+      <c r="B22" s="4">
+        <v>1025306</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22">
+        <v>10</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:8">
+      <c r="A23" s="3">
+        <v>119</v>
+      </c>
+      <c r="B23" s="4">
+        <v>1025401</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23">
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:8">
+      <c r="A24" s="3">
+        <v>120</v>
+      </c>
+      <c r="B24" s="4">
+        <v>1025402</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24">
+        <v>10</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:8">
+      <c r="A25" s="3">
+        <v>121</v>
+      </c>
+      <c r="B25" s="4">
+        <v>1025403</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:8">
+      <c r="A26" s="3">
+        <v>122</v>
+      </c>
+      <c r="B26" s="4">
+        <v>1025404</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26">
+        <v>10</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="1:8">
+      <c r="A27" s="3">
+        <v>123</v>
+      </c>
+      <c r="B27" s="4">
         <v>1025405</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:8">
-      <c r="A8">
-        <v>104</v>
-      </c>
-      <c r="B8" s="3">
-        <v>1025404</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:8">
-      <c r="A9">
-        <v>105</v>
-      </c>
-      <c r="B9" s="3">
-        <v>1025405</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:8">
-      <c r="A10">
-        <v>106</v>
-      </c>
-      <c r="B10" s="3">
+      <c r="C27" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27">
+        <v>10</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:8">
+      <c r="A28" s="3">
+        <v>124</v>
+      </c>
+      <c r="B28" s="4">
         <v>1025406</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
+      <c r="C28" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28">
+        <v>10</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>600</v>
+      </c>
+      <c r="H28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" spans="1:8">
+      <c r="A29" s="3">
+        <v>125</v>
+      </c>
+      <c r="B29" s="4">
+        <v>1025501</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29">
+        <v>10</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
         <v>500</v>
       </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:8">
-      <c r="A11">
-        <v>201</v>
-      </c>
-      <c r="B11" s="4">
-        <v>1025403</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:8">
-      <c r="A12">
-        <v>202</v>
-      </c>
-      <c r="B12" s="4">
-        <v>1025501</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:8">
-      <c r="A13">
-        <v>203</v>
-      </c>
-      <c r="B13" s="4">
+      <c r="H29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" spans="1:8">
+      <c r="A30" s="3">
+        <v>126</v>
+      </c>
+      <c r="B30" s="4">
         <v>1025502</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13">
-        <v>3</v>
-      </c>
-      <c r="G13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:8">
-      <c r="A14">
-        <v>204</v>
-      </c>
-      <c r="B14" s="4">
+      <c r="C30" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30">
+        <v>10</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>500</v>
+      </c>
+      <c r="H30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" spans="1:8">
+      <c r="A31" s="3">
+        <v>127</v>
+      </c>
+      <c r="B31" s="4">
         <v>1025503</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="F14">
-        <v>4</v>
-      </c>
-      <c r="G14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:8">
-      <c r="A15">
-        <v>205</v>
-      </c>
-      <c r="B15" s="4">
+      <c r="C31" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31">
+        <v>10</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>500</v>
+      </c>
+      <c r="H31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" spans="1:8">
+      <c r="A32" s="3">
+        <v>128</v>
+      </c>
+      <c r="B32" s="4">
         <v>1025504</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
-      <c r="F15">
-        <v>5</v>
-      </c>
-      <c r="G15">
+      <c r="C32" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32">
+        <v>10</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>500</v>
+      </c>
+      <c r="H32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="1:8">
+      <c r="A33" s="3">
+        <v>129</v>
+      </c>
+      <c r="B33" s="4">
+        <v>1025505</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33">
+        <v>10</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>500</v>
+      </c>
+      <c r="H33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" spans="1:8">
+      <c r="A34" s="3">
+        <v>130</v>
+      </c>
+      <c r="B34" s="4">
+        <v>1025506</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34">
+        <v>10</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>500</v>
+      </c>
+      <c r="H34">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B6">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8:B10">
+  <conditionalFormatting sqref="B5:B34">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/VisitorGenPaid.xlsx
+++ b/hall/resources/sample/VisitorGenPaid.xlsx
@@ -1814,7 +1814,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" ht="16.5" spans="1:8">
+    <row r="17" ht="16.5" spans="1:7">
       <c r="A17" s="3">
         <v>113</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="18" ht="16.5" spans="1:8">
+    <row r="18" ht="16.5" spans="1:7">
       <c r="A18" s="3">
         <v>114</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="19" ht="16.5" spans="1:8">
+    <row r="19" ht="16.5" spans="1:7">
       <c r="A19" s="3">
         <v>115</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="20" ht="16.5" spans="1:8">
+    <row r="20" ht="16.5" spans="1:7">
       <c r="A20" s="3">
         <v>116</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="21" ht="16.5" spans="1:8">
+    <row r="21" ht="16.5" spans="1:7">
       <c r="A21" s="3">
         <v>117</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="22" ht="16.5" spans="1:8">
+    <row r="22" ht="16.5" spans="1:7">
       <c r="A22" s="3">
         <v>118</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="23" ht="16.5" spans="1:8">
+    <row r="23" ht="16.5" spans="1:7">
       <c r="A23" s="3">
         <v>119</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="24" ht="16.5" spans="1:8">
+    <row r="24" ht="16.5" spans="1:7">
       <c r="A24" s="3">
         <v>120</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="25" ht="16.5" spans="1:8">
+    <row r="25" ht="16.5" spans="1:7">
       <c r="A25" s="3">
         <v>121</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="26" ht="16.5" spans="1:8">
+    <row r="26" ht="16.5" spans="1:7">
       <c r="A26" s="3">
         <v>122</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="27" ht="16.5" spans="1:8">
+    <row r="27" ht="16.5" spans="1:7">
       <c r="A27" s="3">
         <v>123</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="28" ht="16.5" spans="1:8">
+    <row r="28" ht="16.5" spans="1:7">
       <c r="A28" s="3">
         <v>124</v>
       </c>
@@ -2089,11 +2089,8 @@
       <c r="G28">
         <v>600</v>
       </c>
-      <c r="H28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" spans="1:8">
+    </row>
+    <row r="29" ht="16.5" spans="1:7">
       <c r="A29" s="3">
         <v>125</v>
       </c>
@@ -2115,11 +2112,8 @@
       <c r="G29">
         <v>500</v>
       </c>
-      <c r="H29">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" ht="16.5" spans="1:8">
+    </row>
+    <row r="30" ht="16.5" spans="1:7">
       <c r="A30" s="3">
         <v>126</v>
       </c>
@@ -2141,11 +2135,8 @@
       <c r="G30">
         <v>500</v>
       </c>
-      <c r="H30">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" spans="1:8">
+    </row>
+    <row r="31" ht="16.5" spans="1:7">
       <c r="A31" s="3">
         <v>127</v>
       </c>
@@ -2167,11 +2158,8 @@
       <c r="G31">
         <v>500</v>
       </c>
-      <c r="H31">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5" spans="1:8">
+    </row>
+    <row r="32" ht="16.5" spans="1:7">
       <c r="A32" s="3">
         <v>128</v>
       </c>
@@ -2193,11 +2181,8 @@
       <c r="G32">
         <v>500</v>
       </c>
-      <c r="H32">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" ht="16.5" spans="1:8">
+    </row>
+    <row r="33" ht="16.5" spans="1:7">
       <c r="A33" s="3">
         <v>129</v>
       </c>
@@ -2219,11 +2204,8 @@
       <c r="G33">
         <v>500</v>
       </c>
-      <c r="H33">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" ht="16.5" spans="1:8">
+    </row>
+    <row r="34" ht="16.5" spans="1:7">
       <c r="A34" s="3">
         <v>130</v>
       </c>
@@ -2244,9 +2226,6 @@
       </c>
       <c r="G34">
         <v>500</v>
-      </c>
-      <c r="H34">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/VisitorGenPaid.xlsx
+++ b/hall/resources/sample/VisitorGenPaid.xlsx
@@ -60,6 +60,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+若是价格类型字段填了2-美刀；则该字段需要填写ShopRechargeList表中的ID</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="I1" authorId="0">
       <text>
         <r>
@@ -87,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="53">
   <si>
     <t>序号ID</t>
   </si>
@@ -117,9 +139,6 @@
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>BigDecimal</t>
   </si>
   <si>
     <t>string</t>
@@ -1506,36 +1525,36 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:9">
@@ -1546,10 +1565,10 @@
         <v>1025101</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
         <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -1569,10 +1588,10 @@
         <v>1025102</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>10</v>
@@ -1592,10 +1611,10 @@
         <v>1025103</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>10</v>
@@ -1615,10 +1634,10 @@
         <v>1025104</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8">
         <v>10</v>
@@ -1638,10 +1657,10 @@
         <v>1025105</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9">
         <v>10</v>
@@ -1661,10 +1680,10 @@
         <v>1025106</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E10">
         <v>10</v>
@@ -1684,10 +1703,10 @@
         <v>1025201</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
         <v>26</v>
-      </c>
-      <c r="D11" t="s">
-        <v>27</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1707,10 +1726,10 @@
         <v>1025202</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12">
         <v>10</v>
@@ -1730,10 +1749,10 @@
         <v>1025203</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13">
         <v>10</v>
@@ -1753,10 +1772,10 @@
         <v>1025204</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14">
         <v>10</v>
@@ -1776,10 +1795,10 @@
         <v>1025205</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -1799,10 +1818,10 @@
         <v>1025206</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16">
         <v>10</v>
@@ -1822,10 +1841,10 @@
         <v>1025301</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s">
         <v>33</v>
-      </c>
-      <c r="D17" t="s">
-        <v>34</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -1845,10 +1864,10 @@
         <v>1025302</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18">
         <v>10</v>
@@ -1868,10 +1887,10 @@
         <v>1025303</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E19">
         <v>10</v>
@@ -1891,10 +1910,10 @@
         <v>1025304</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20">
         <v>10</v>
@@ -1914,10 +1933,10 @@
         <v>1025305</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E21">
         <v>10</v>
@@ -1937,10 +1956,10 @@
         <v>1025306</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E22">
         <v>10</v>
@@ -1960,10 +1979,10 @@
         <v>1025401</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" t="s">
         <v>40</v>
-      </c>
-      <c r="D23" t="s">
-        <v>41</v>
       </c>
       <c r="E23">
         <v>10</v>
@@ -1983,10 +2002,10 @@
         <v>1025402</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E24">
         <v>10</v>
@@ -2006,10 +2025,10 @@
         <v>1025403</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E25">
         <v>10</v>
@@ -2029,10 +2048,10 @@
         <v>1025404</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E26">
         <v>10</v>
@@ -2052,10 +2071,10 @@
         <v>1025405</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E27">
         <v>10</v>
@@ -2075,10 +2094,10 @@
         <v>1025406</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E28">
         <v>10</v>
@@ -2098,10 +2117,10 @@
         <v>1025501</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" t="s">
         <v>47</v>
-      </c>
-      <c r="D29" t="s">
-        <v>48</v>
       </c>
       <c r="E29">
         <v>10</v>
@@ -2121,10 +2140,10 @@
         <v>1025502</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30">
         <v>10</v>
@@ -2144,10 +2163,10 @@
         <v>1025503</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E31">
         <v>10</v>
@@ -2167,10 +2186,10 @@
         <v>1025504</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E32">
         <v>10</v>
@@ -2190,10 +2209,10 @@
         <v>1025505</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E33">
         <v>10</v>
@@ -2213,10 +2232,10 @@
         <v>1025506</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E34">
         <v>10</v>
